--- a/3_ml_model/analysis/data/PRISM_vs_nmr.xlsx
+++ b/3_ml_model/analysis/data/PRISM_vs_nmr.xlsx
@@ -2,15 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -50,7 +49,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -413,8 +412,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K153"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:K154"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -493,10 +492,6 @@
       <c r="E2" t="n">
         <v>450.4806</v>
       </c>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
           <t>slow</t>
@@ -528,10 +523,6 @@
       <c r="E3" t="n">
         <v>7.3677</v>
       </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
           <t>slow</t>
@@ -653,10 +644,6 @@
       <c r="E6" t="n">
         <v>3.7037</v>
       </c>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
           <t>slow</t>
@@ -733,10 +720,6 @@
       <c r="E8" t="n">
         <v>0.9247</v>
       </c>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
           <t>slow</t>
@@ -858,10 +841,6 @@
       <c r="E11" t="n">
         <v>0.8433</v>
       </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
           <t>slow</t>
@@ -893,10 +872,6 @@
       <c r="E12" t="n">
         <v>2.2247</v>
       </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
           <t>slow</t>
@@ -1018,10 +993,6 @@
       <c r="E15" t="n">
         <v>1.3934</v>
       </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
           <t>slow</t>
@@ -1053,10 +1024,6 @@
       <c r="E16" t="n">
         <v>6.7246</v>
       </c>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
           <t>slow</t>
@@ -1088,10 +1055,6 @@
       <c r="E17" t="n">
         <v>1.9221</v>
       </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
           <t>slow</t>
@@ -1123,10 +1086,6 @@
       <c r="E18" t="n">
         <v>0.4488</v>
       </c>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
           <t>slow</t>
@@ -1248,10 +1207,6 @@
       <c r="E21" t="n">
         <v>5.3957</v>
       </c>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
           <t>slow</t>
@@ -1373,10 +1328,6 @@
       <c r="E24" t="n">
         <v>3.579</v>
       </c>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr">
         <is>
           <t>slow</t>
@@ -1453,10 +1404,6 @@
       <c r="E26" t="n">
         <v>0.3256</v>
       </c>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
         <is>
           <t>slow</t>
@@ -1488,10 +1435,6 @@
       <c r="E27" t="n">
         <v>0.9864000000000001</v>
       </c>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr">
         <is>
           <t>slow</t>
@@ -1523,10 +1466,6 @@
       <c r="E28" t="n">
         <v>3.7341</v>
       </c>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr">
         <is>
           <t>slow</t>
@@ -1558,10 +1497,6 @@
       <c r="E29" t="n">
         <v>0.5023</v>
       </c>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr">
         <is>
           <t>slow</t>
@@ -1593,10 +1528,6 @@
       <c r="E30" t="n">
         <v>0.3706</v>
       </c>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr">
         <is>
           <t>slow</t>
@@ -1611,27 +1542,23 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>rxn_01_35</t>
+          <t>rxn_01_34</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>1</v>
       </c>
       <c r="C31" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Acid chloride 1 + Amine 35</t>
+          <t>Acid chloride 1 + Amine 34</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4.0083</v>
-      </c>
-      <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
+        <v>73.464</v>
+      </c>
       <c r="J31" t="inlineStr">
         <is>
           <t>slow</t>
@@ -1646,27 +1573,23 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>rxn_01_36</t>
+          <t>rxn_01_35</t>
         </is>
       </c>
       <c r="B32" t="n">
         <v>1</v>
       </c>
       <c r="C32" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Acid chloride 1 + Amine 36</t>
+          <t>Acid chloride 1 + Amine 35</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>0.1288</v>
-      </c>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr"/>
+        <v>4.0083</v>
+      </c>
       <c r="J32" t="inlineStr">
         <is>
           <t>slow</t>
@@ -1681,70 +1604,56 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>rxn_02_03</t>
+          <t>rxn_01_36</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C33" t="n">
-        <v>3</v>
+        <v>36</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Amine 3 + Acid Chloride 2</t>
+          <t>Acid chloride 1 + Amine 36</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6.8476</v>
-      </c>
-      <c r="F33" t="n">
-        <v>6.530612244897961</v>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>low_confidence_order_of_magnitude</t>
-        </is>
-      </c>
-      <c r="H33" t="n">
-        <v>1</v>
-      </c>
-      <c r="I33" t="n">
-        <v>1</v>
+        <v>0.1288</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>measurable</t>
+          <t>slow</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>k_corrected &gt; 0</t>
+          <t>unmeasurable workbook bin</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>rxn_03_03</t>
+          <t>rxn_02_03</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C34" t="n">
         <v>3</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Amine 3 + Acid Chloride 3</t>
+          <t>Amine 3 + Acid Chloride 2</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>8.224399999999999</v>
+        <v>6.8476</v>
       </c>
       <c r="F34" t="n">
-        <v>4.740740740740738</v>
+        <v>6.530612244897961</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1771,142 +1680,144 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>rxn_04_03</t>
+          <t>rxn_03_03</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C35" t="n">
         <v>3</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Amine 3 + Acid Chloride 4</t>
+          <t>Amine 3 + Acid Chloride 3</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>68.3126</v>
-      </c>
-      <c r="F35" t="inlineStr"/>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
+        <v>8.224399999999999</v>
+      </c>
+      <c r="F35" t="n">
+        <v>4.740740740740738</v>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>low_confidence_order_of_magnitude</t>
+        </is>
+      </c>
+      <c r="H35" t="n">
+        <v>1</v>
+      </c>
+      <c r="I35" t="n">
+        <v>1</v>
+      </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>instant</t>
+          <t>measurable</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>unmeasurable workbook bin</t>
+          <t>k_corrected &gt; 0</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>rxn_05_03</t>
+          <t>rxn_04_03</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C36" t="n">
         <v>3</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Amine 3 + Acid Chloride 5</t>
+          <t>Amine 3 + Acid Chloride 4</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>24.5018</v>
-      </c>
-      <c r="F36" t="n">
-        <v>71.11111111111106</v>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>low_confidence_order_of_magnitude</t>
-        </is>
-      </c>
-      <c r="H36" t="n">
-        <v>1</v>
-      </c>
-      <c r="I36" t="n">
-        <v>1</v>
+        <v>68.3126</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>measurable</t>
+          <t>instant</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>k_corrected &gt; 0</t>
+          <t>unmeasurable workbook bin</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>rxn_06_03</t>
+          <t>rxn_05_03</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C37" t="n">
         <v>3</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Amine 3 + Acid Chloride 6</t>
+          <t>Amine 3 + Acid Chloride 5</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>10.327</v>
-      </c>
-      <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr"/>
+        <v>24.5018</v>
+      </c>
+      <c r="F37" t="n">
+        <v>71.11111111111106</v>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>low_confidence_order_of_magnitude</t>
+        </is>
+      </c>
+      <c r="H37" t="n">
+        <v>1</v>
+      </c>
+      <c r="I37" t="n">
+        <v>1</v>
+      </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>measurable</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>unmeasurable workbook bin</t>
+          <t>k_corrected &gt; 0</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>rxn_07_03</t>
+          <t>rxn_06_03</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C38" t="n">
         <v>3</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Amine 3 + Acid Chloride 7</t>
+          <t>Amine 3 + Acid Chloride 6</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4.1765</v>
-      </c>
-      <c r="F38" t="inlineStr"/>
-      <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr"/>
-      <c r="I38" t="inlineStr"/>
+        <v>10.327</v>
+      </c>
       <c r="J38" t="inlineStr">
         <is>
           <t>slow</t>
@@ -1921,230 +1832,208 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>rxn_08_03</t>
+          <t>rxn_07_03</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C39" t="n">
         <v>3</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Amine 3 + Acid Chloride 8</t>
+          <t>Amine 3 + Acid Chloride 7</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>10.3793</v>
-      </c>
-      <c r="F39" t="n">
-        <v>7.352138307552321</v>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>medium_confidence</t>
-        </is>
-      </c>
-      <c r="H39" t="n">
-        <v>1</v>
-      </c>
-      <c r="I39" t="n">
-        <v>1</v>
+        <v>4.1765</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>measurable</t>
+          <t>slow</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>k_corrected &gt; 0</t>
+          <t>unmeasurable workbook bin</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>rxn_09_03</t>
+          <t>rxn_08_03</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C40" t="n">
         <v>3</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Amine 3 + Acid Chloride 9</t>
+          <t>Amine 3 + Acid Chloride 8</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>3.2689</v>
-      </c>
-      <c r="F40" t="inlineStr"/>
-      <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr"/>
-      <c r="I40" t="inlineStr"/>
+        <v>10.3793</v>
+      </c>
+      <c r="F40" t="n">
+        <v>7.352138307552321</v>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>medium_confidence</t>
+        </is>
+      </c>
+      <c r="H40" t="n">
+        <v>1</v>
+      </c>
+      <c r="I40" t="n">
+        <v>1</v>
+      </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>measurable</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>unmeasurable workbook bin</t>
+          <t>k_corrected &gt; 0</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>rxn_10_03</t>
+          <t>rxn_09_03</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C41" t="n">
         <v>3</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Amine 3 + Acid Chloride 10</t>
+          <t>Amine 3 + Acid Chloride 9</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>17.0357</v>
-      </c>
-      <c r="F41" t="n">
-        <v>12.30769230769231</v>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>low_confidence_order_of_magnitude</t>
-        </is>
-      </c>
-      <c r="H41" t="n">
-        <v>1</v>
-      </c>
-      <c r="I41" t="n">
-        <v>1</v>
+        <v>3.2689</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>measurable</t>
+          <t>slow</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>k_corrected &gt; 0</t>
+          <t>unmeasurable workbook bin</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>rxn_11_03</t>
+          <t>rxn_10_03</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C42" t="n">
         <v>3</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Amine 3 + Acid Chloride 11</t>
+          <t>Amine 3 + Acid Chloride 10</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>59.1295</v>
-      </c>
-      <c r="F42" t="inlineStr"/>
-      <c r="G42" t="inlineStr"/>
-      <c r="H42" t="inlineStr"/>
-      <c r="I42" t="inlineStr"/>
+        <v>17.0357</v>
+      </c>
+      <c r="F42" t="n">
+        <v>12.30769230769231</v>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>low_confidence_order_of_magnitude</t>
+        </is>
+      </c>
+      <c r="H42" t="n">
+        <v>1</v>
+      </c>
+      <c r="I42" t="n">
+        <v>1</v>
+      </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>measurable</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>unmeasurable workbook bin</t>
+          <t>k_corrected &gt; 0</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>rxn_12_03</t>
+          <t>rxn_11_03</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C43" t="n">
         <v>3</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Amine 3 + Acid Chloride 12</t>
+          <t>Amine 3 + Acid Chloride 11</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>15.4861</v>
-      </c>
-      <c r="F43" t="n">
-        <v>11.85185185185185</v>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>low_confidence_order_of_magnitude</t>
-        </is>
-      </c>
-      <c r="H43" t="n">
-        <v>1</v>
-      </c>
-      <c r="I43" t="n">
-        <v>1</v>
+        <v>59.1295</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>measurable</t>
+          <t>slow</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>k_corrected &gt; 0</t>
+          <t>unmeasurable workbook bin</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>rxn_13_03</t>
+          <t>rxn_12_03</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C44" t="n">
         <v>3</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Amine 3 + Acid Chloride 13</t>
+          <t>Amine 3 + Acid Chloride 12</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>65.768</v>
+        <v>15.4861</v>
       </c>
       <c r="F44" t="n">
-        <v>232.7272727272725</v>
+        <v>11.85185185185185</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -2171,25 +2060,25 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>rxn_14_03</t>
+          <t>rxn_13_03</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C45" t="n">
         <v>3</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Amine 3 + Acid Chloride 14</t>
+          <t>Amine 3 + Acid Chloride 13</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>433.5306</v>
+        <v>65.768</v>
       </c>
       <c r="F45" t="n">
-        <v>853.3333333333331</v>
+        <v>232.7272727272725</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -2216,29 +2105,29 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>rxn_15_03</t>
+          <t>rxn_14_03</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C46" t="n">
         <v>3</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Amine 3 + Acid Chloride 15</t>
+          <t>Amine 3 + Acid Chloride 14</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>13.4499</v>
+        <v>433.5306</v>
       </c>
       <c r="F46" t="n">
-        <v>16.69591758870661</v>
+        <v>853.3333333333331</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>high_confidence</t>
+          <t>low_confidence_order_of_magnitude</t>
         </is>
       </c>
       <c r="H46" t="n">
@@ -2261,109 +2150,105 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>rxn_16_03</t>
+          <t>rxn_15_03</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C47" t="n">
         <v>3</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Amine 3 + Acid Chloride 16</t>
+          <t>Amine 3 + Acid Chloride 15</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4.4171</v>
-      </c>
-      <c r="F47" t="inlineStr"/>
-      <c r="G47" t="inlineStr"/>
-      <c r="H47" t="inlineStr"/>
-      <c r="I47" t="inlineStr"/>
+        <v>13.4499</v>
+      </c>
+      <c r="F47" t="n">
+        <v>16.69591758870661</v>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>high_confidence</t>
+        </is>
+      </c>
+      <c r="H47" t="n">
+        <v>1</v>
+      </c>
+      <c r="I47" t="n">
+        <v>1</v>
+      </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>measurable</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>unmeasurable workbook bin</t>
+          <t>k_corrected &gt; 0</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>rxn_18_03</t>
+          <t>rxn_16_03</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C48" t="n">
         <v>3</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Amine 3 + Acid Chloride 18</t>
+          <t>Amine 3 + Acid Chloride 16</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5.6282</v>
-      </c>
-      <c r="F48" t="n">
-        <v>7.485380116959067</v>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>low_confidence_order_of_magnitude</t>
-        </is>
-      </c>
-      <c r="H48" t="n">
-        <v>1</v>
-      </c>
-      <c r="I48" t="n">
-        <v>1</v>
+        <v>4.4171</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>measurable</t>
+          <t>slow</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>k_corrected &gt; 0</t>
+          <t>unmeasurable workbook bin</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>rxn_19_03</t>
+          <t>rxn_18_03</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C49" t="n">
         <v>3</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Amine 3 + Acid Chloride 19</t>
+          <t>Amine 3 + Acid Chloride 18</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>20.7746</v>
+        <v>5.6282</v>
       </c>
       <c r="F49" t="n">
-        <v>34.60968163977325</v>
+        <v>7.485380116959067</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>medium_confidence</t>
+          <t>low_confidence_order_of_magnitude</t>
         </is>
       </c>
       <c r="H49" t="n">
@@ -2386,65 +2271,71 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>rxn_20_03</t>
+          <t>rxn_19_03</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C50" t="n">
         <v>3</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Amine 3 + Acid Chloride 20</t>
+          <t>Amine 3 + Acid Chloride 19</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>9.470800000000001</v>
-      </c>
-      <c r="F50" t="inlineStr"/>
-      <c r="G50" t="inlineStr"/>
-      <c r="H50" t="inlineStr"/>
-      <c r="I50" t="inlineStr"/>
+        <v>20.7746</v>
+      </c>
+      <c r="F50" t="n">
+        <v>34.60968163977325</v>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>medium_confidence</t>
+        </is>
+      </c>
+      <c r="H50" t="n">
+        <v>1</v>
+      </c>
+      <c r="I50" t="n">
+        <v>1</v>
+      </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>measurable</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>unmeasurable workbook bin</t>
+          <t>k_corrected &gt; 0</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>rxn_21_03</t>
+          <t>rxn_20_03</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C51" t="n">
         <v>3</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Amine 3 + Acid Chloride 21</t>
+          <t>Amine 3 + Acid Chloride 20</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>386.9511</v>
-      </c>
-      <c r="F51" t="inlineStr"/>
-      <c r="G51" t="inlineStr"/>
-      <c r="H51" t="inlineStr"/>
-      <c r="I51" t="inlineStr"/>
+        <v>9.470800000000001</v>
+      </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>instant</t>
+          <t>slow</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -2456,70 +2347,56 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>rxn_22_03</t>
+          <t>rxn_21_03</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C52" t="n">
         <v>3</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Amine 3 + Acid Chloride 22</t>
+          <t>Amine 3 + Acid Chloride 21</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>11.0279</v>
-      </c>
-      <c r="F52" t="n">
-        <v>7.61904761904762</v>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>low_confidence_order_of_magnitude</t>
-        </is>
-      </c>
-      <c r="H52" t="n">
-        <v>1</v>
-      </c>
-      <c r="I52" t="n">
-        <v>1</v>
+        <v>386.9511</v>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>measurable</t>
+          <t>instant</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>k_corrected &gt; 0</t>
+          <t>unmeasurable workbook bin</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>rxn_23_03</t>
+          <t>rxn_22_03</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C53" t="n">
         <v>3</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Amine 3 + Acid Chloride 23</t>
+          <t>Amine 3 + Acid Chloride 22</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>7.1149</v>
+        <v>11.0279</v>
       </c>
       <c r="F53" t="n">
-        <v>13.33333333333335</v>
+        <v>7.61904761904762</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -2546,62 +2423,68 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>rxn_24_03</t>
+          <t>rxn_23_03</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C54" t="n">
         <v>3</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Amine 3 + Acid Chloride 24</t>
+          <t>Amine 3 + Acid Chloride 23</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>3.6466</v>
-      </c>
-      <c r="F54" t="inlineStr"/>
-      <c r="G54" t="inlineStr"/>
-      <c r="H54" t="inlineStr"/>
-      <c r="I54" t="inlineStr"/>
+        <v>7.1149</v>
+      </c>
+      <c r="F54" t="n">
+        <v>13.33333333333335</v>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>low_confidence_order_of_magnitude</t>
+        </is>
+      </c>
+      <c r="H54" t="n">
+        <v>1</v>
+      </c>
+      <c r="I54" t="n">
+        <v>1</v>
+      </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>measurable</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>unmeasurable workbook bin</t>
+          <t>k_corrected &gt; 0</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>rxn_25_03</t>
+          <t>rxn_24_03</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C55" t="n">
         <v>3</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Amine 3 + Acid Chloride 25</t>
+          <t>Amine 3 + Acid Chloride 24</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>101.8586</v>
-      </c>
-      <c r="F55" t="inlineStr"/>
-      <c r="G55" t="inlineStr"/>
-      <c r="H55" t="inlineStr"/>
-      <c r="I55" t="inlineStr"/>
+        <v>3.6466</v>
+      </c>
       <c r="J55" t="inlineStr">
         <is>
           <t>slow</t>
@@ -2616,150 +2499,132 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>rxn_26_03</t>
+          <t>rxn_25_03</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C56" t="n">
         <v>3</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Amine 3 + Acid Chloride 26</t>
+          <t>Amine 3 + Acid Chloride 25</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>50.7315</v>
-      </c>
-      <c r="F56" t="n">
-        <v>105.019305019305</v>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>medium_confidence</t>
-        </is>
-      </c>
-      <c r="H56" t="n">
-        <v>1</v>
-      </c>
-      <c r="I56" t="n">
-        <v>1</v>
+        <v>101.8586</v>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>measurable</t>
+          <t>slow</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>k_corrected &gt; 0</t>
+          <t>unmeasurable workbook bin</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>rxn_27_03</t>
+          <t>rxn_26_03</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C57" t="n">
         <v>3</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Amine 3 + Acid Chloride 27</t>
+          <t>Amine 3 + Acid Chloride 26</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>147.7759</v>
-      </c>
-      <c r="F57" t="inlineStr"/>
-      <c r="G57" t="inlineStr"/>
-      <c r="H57" t="inlineStr"/>
-      <c r="I57" t="inlineStr"/>
+        <v>50.7315</v>
+      </c>
+      <c r="F57" t="n">
+        <v>105.019305019305</v>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>medium_confidence</t>
+        </is>
+      </c>
+      <c r="H57" t="n">
+        <v>1</v>
+      </c>
+      <c r="I57" t="n">
+        <v>1</v>
+      </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>measurable</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>unmeasurable workbook bin</t>
+          <t>k_corrected &gt; 0</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>rxn_28_03</t>
+          <t>rxn_27_03</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C58" t="n">
         <v>3</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Amine 3 + Acid Chloride 28</t>
+          <t>Amine 3 + Acid Chloride 27</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>12.9576</v>
-      </c>
-      <c r="F58" t="n">
-        <v>20.97491717936583</v>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>medium_confidence</t>
-        </is>
-      </c>
-      <c r="H58" t="n">
-        <v>1</v>
-      </c>
-      <c r="I58" t="n">
-        <v>1</v>
+        <v>147.7759</v>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>measurable</t>
+          <t>slow</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>k_corrected &gt; 0</t>
+          <t>unmeasurable workbook bin</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>rxn_29_03</t>
+          <t>rxn_28_03</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C59" t="n">
         <v>3</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Amine 3 + Acid Chloride 29</t>
+          <t>Amine 3 + Acid Chloride 28</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>7.3954</v>
+        <v>12.9576</v>
       </c>
       <c r="F59" t="n">
-        <v>4.92860057119543</v>
+        <v>20.97491717936583</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -2786,29 +2651,29 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>rxn_30_03</t>
+          <t>rxn_29_03</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C60" t="n">
         <v>3</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Amine 3 + Acid Chloride 30</t>
+          <t>Amine 3 + Acid Chloride 29</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>113.83</v>
+        <v>7.3954</v>
       </c>
       <c r="F60" t="n">
-        <v>160.0000000000001</v>
+        <v>4.92860057119543</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>low_confidence_order_of_magnitude</t>
+          <t>medium_confidence</t>
         </is>
       </c>
       <c r="H60" t="n">
@@ -2831,29 +2696,29 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>rxn_31_03</t>
+          <t>rxn_30_03</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C61" t="n">
         <v>3</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Amine 3 + Acid Chloride 31</t>
+          <t>Amine 3 + Acid Chloride 30</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>12.4844</v>
+        <v>113.83</v>
       </c>
       <c r="F61" t="n">
-        <v>27.09578544061302</v>
+        <v>160.0000000000001</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>high_confidence</t>
+          <t>low_confidence_order_of_magnitude</t>
         </is>
       </c>
       <c r="H61" t="n">
@@ -2876,1201 +2741,991 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>rxn_01_37</t>
+          <t>rxn_31_03</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="C62" t="n">
-        <v>37</v>
+        <v>3</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Amine 37 + Acid Chloride 1</t>
+          <t>Amine 3 + Acid Chloride 31</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>11.833</v>
-      </c>
-      <c r="F62" t="inlineStr"/>
-      <c r="G62" t="inlineStr"/>
-      <c r="H62" t="inlineStr"/>
-      <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
+        <v>12.4844</v>
+      </c>
+      <c r="F62" t="n">
+        <v>27.09578544061302</v>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>high_confidence</t>
+        </is>
+      </c>
+      <c r="H62" t="n">
+        <v>1</v>
+      </c>
+      <c r="I62" t="n">
+        <v>1</v>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>measurable</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>k_corrected &gt; 0</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>rxn_02_37</t>
+          <t>rxn_01_37</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C63" t="n">
         <v>37</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Amine 37 + Acid chloride 2</t>
+          <t>Amine 37 + Acid Chloride 1</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>12.5752</v>
-      </c>
-      <c r="F63" t="inlineStr"/>
-      <c r="G63" t="inlineStr"/>
-      <c r="H63" t="inlineStr"/>
-      <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr"/>
-      <c r="K63" t="inlineStr"/>
+        <v>11.833</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>rxn_03_37</t>
+          <t>rxn_02_37</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C64" t="n">
         <v>37</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Amine 37 + Acid chloride 3</t>
+          <t>Amine 37 + Acid chloride 2</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>5.4307</v>
-      </c>
-      <c r="F64" t="inlineStr"/>
-      <c r="G64" t="inlineStr"/>
-      <c r="H64" t="inlineStr"/>
-      <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
+        <v>12.5752</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>rxn_04_37</t>
+          <t>rxn_03_37</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C65" t="n">
         <v>37</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Amine 37 + Acid chloride 4</t>
+          <t>Amine 37 + Acid chloride 3</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>101.3</v>
-      </c>
-      <c r="F65" t="inlineStr"/>
-      <c r="G65" t="inlineStr"/>
-      <c r="H65" t="inlineStr"/>
-      <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
+        <v>5.4307</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>rxn_05_37</t>
+          <t>rxn_04_37</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C66" t="n">
         <v>37</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Amine 37 + Acid chloride 5</t>
+          <t>Amine 37 + Acid chloride 4</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>20.2119</v>
-      </c>
-      <c r="F66" t="inlineStr"/>
-      <c r="G66" t="inlineStr"/>
-      <c r="H66" t="inlineStr"/>
-      <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
+        <v>7.091</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>rxn_06_37</t>
+          <t>rxn_05_37</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C67" t="n">
         <v>37</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Amine 37 + Acid chloride 6</t>
+          <t>Amine 37 + Acid chloride 5</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>8.190099999999999</v>
-      </c>
-      <c r="F67" t="inlineStr"/>
-      <c r="G67" t="inlineStr"/>
-      <c r="H67" t="inlineStr"/>
-      <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
+        <v>20.2119</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>rxn_07_37</t>
+          <t>rxn_06_37</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C68" t="n">
         <v>37</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Amine 37 + Acid chloride 7</t>
+          <t>Amine 37 + Acid chloride 6</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>3.3328</v>
-      </c>
-      <c r="F68" t="inlineStr"/>
-      <c r="G68" t="inlineStr"/>
-      <c r="H68" t="inlineStr"/>
-      <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
+        <v>8.190099999999999</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>rxn_08_37</t>
+          <t>rxn_07_37</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C69" t="n">
         <v>37</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Amine 37 + Acid chloride 8</t>
+          <t>Amine 37 + Acid chloride 7</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>11.7187</v>
-      </c>
-      <c r="F69" t="inlineStr"/>
-      <c r="G69" t="inlineStr"/>
-      <c r="H69" t="inlineStr"/>
-      <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
+        <v>3.3328</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>rxn_09_37</t>
+          <t>rxn_08_37</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C70" t="n">
         <v>37</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Amine 37 + Acid chloride 9</t>
+          <t>Amine 37 + Acid chloride 8</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>2.5031</v>
-      </c>
-      <c r="F70" t="inlineStr"/>
-      <c r="G70" t="inlineStr"/>
-      <c r="H70" t="inlineStr"/>
-      <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
+        <v>11.7187</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>rxn_10_37</t>
+          <t>rxn_09_37</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C71" t="n">
         <v>37</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Amine 37 + Acid chloride 10</t>
+          <t>Amine 37 + Acid chloride 9</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>18.9535</v>
-      </c>
-      <c r="F71" t="inlineStr"/>
-      <c r="G71" t="inlineStr"/>
-      <c r="H71" t="inlineStr"/>
-      <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
+        <v>2.5031</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>rxn_11_37</t>
+          <t>rxn_10_37</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C72" t="n">
         <v>37</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Amine 37 + Acid chloride 11</t>
+          <t>Amine 37 + Acid chloride 10</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>29.1732</v>
-      </c>
-      <c r="F72" t="inlineStr"/>
-      <c r="G72" t="inlineStr"/>
-      <c r="H72" t="inlineStr"/>
-      <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr"/>
-      <c r="K72" t="inlineStr"/>
+        <v>18.9535</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>rxn_12_37</t>
+          <t>rxn_11_37</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C73" t="n">
         <v>37</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Amine 37 + Acid chloride 12</t>
+          <t>Amine 37 + Acid chloride 11</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>19.2354</v>
-      </c>
-      <c r="F73" t="inlineStr"/>
-      <c r="G73" t="inlineStr"/>
-      <c r="H73" t="inlineStr"/>
-      <c r="I73" t="inlineStr"/>
-      <c r="J73" t="inlineStr"/>
-      <c r="K73" t="inlineStr"/>
+        <v>29.1732</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>rxn_13_37</t>
+          <t>rxn_12_37</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C74" t="n">
         <v>37</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Amine 37 + Acid chloride 13</t>
+          <t>Amine 37 + Acid chloride 12</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>67.672</v>
-      </c>
-      <c r="F74" t="inlineStr"/>
-      <c r="G74" t="inlineStr"/>
-      <c r="H74" t="inlineStr"/>
-      <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr"/>
-      <c r="K74" t="inlineStr"/>
+        <v>19.2354</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>rxn_14_37</t>
+          <t>rxn_13_37</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C75" t="n">
         <v>37</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Amine 37 + Acid chloride 14</t>
+          <t>Amine 37 + Acid chloride 13</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>835.2252</v>
-      </c>
-      <c r="F75" t="inlineStr"/>
-      <c r="G75" t="inlineStr"/>
-      <c r="H75" t="inlineStr"/>
-      <c r="I75" t="inlineStr"/>
-      <c r="J75" t="inlineStr"/>
-      <c r="K75" t="inlineStr"/>
+        <v>67.672</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>rxn_15_37</t>
+          <t>rxn_14_37</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C76" t="n">
         <v>37</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Amine 37 + Acid chloride 15</t>
+          <t>Amine 37 + Acid chloride 14</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>14.2472</v>
-      </c>
-      <c r="F76" t="inlineStr"/>
-      <c r="G76" t="inlineStr"/>
-      <c r="H76" t="inlineStr"/>
-      <c r="I76" t="inlineStr"/>
-      <c r="J76" t="inlineStr"/>
-      <c r="K76" t="inlineStr"/>
+        <v>835.2252</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>rxn_16_37</t>
+          <t>rxn_15_37</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C77" t="n">
         <v>37</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Amine 37 + Acid chloride 16</t>
+          <t>Amine 37 + Acid chloride 15</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>5.9037</v>
-      </c>
-      <c r="F77" t="inlineStr"/>
-      <c r="G77" t="inlineStr"/>
-      <c r="H77" t="inlineStr"/>
-      <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr"/>
-      <c r="K77" t="inlineStr"/>
+        <v>14.2472</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>rxn_17_37</t>
+          <t>rxn_16_37</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C78" t="n">
         <v>37</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Amine 37 + Acid chloride 17</t>
+          <t>Amine 37 + Acid chloride 16</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>23.6269</v>
-      </c>
-      <c r="F78" t="inlineStr"/>
-      <c r="G78" t="inlineStr"/>
-      <c r="H78" t="inlineStr"/>
-      <c r="I78" t="inlineStr"/>
-      <c r="J78" t="inlineStr"/>
-      <c r="K78" t="inlineStr"/>
+        <v>5.9037</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>rxn_18_37</t>
+          <t>rxn_17_37</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C79" t="n">
         <v>37</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Amine 37 + Acid chloride 18</t>
+          <t>Amine 37 + Acid chloride 17</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>5.0835</v>
-      </c>
-      <c r="F79" t="inlineStr"/>
-      <c r="G79" t="inlineStr"/>
-      <c r="H79" t="inlineStr"/>
-      <c r="I79" t="inlineStr"/>
-      <c r="J79" t="inlineStr"/>
-      <c r="K79" t="inlineStr"/>
+        <v>23.6269</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>rxn_19_37</t>
+          <t>rxn_18_37</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C80" t="n">
         <v>37</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Amine 37 + Acid chloride 19</t>
+          <t>Amine 37 + Acid chloride 18</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>22.4479</v>
-      </c>
-      <c r="F80" t="inlineStr"/>
-      <c r="G80" t="inlineStr"/>
-      <c r="H80" t="inlineStr"/>
-      <c r="I80" t="inlineStr"/>
-      <c r="J80" t="inlineStr"/>
-      <c r="K80" t="inlineStr"/>
+        <v>5.0835</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>rxn_20_37</t>
+          <t>rxn_19_37</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C81" t="n">
         <v>37</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Amine 37 + Acid chloride 20</t>
+          <t>Amine 37 + Acid chloride 19</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>15.8582</v>
-      </c>
-      <c r="F81" t="inlineStr"/>
-      <c r="G81" t="inlineStr"/>
-      <c r="H81" t="inlineStr"/>
-      <c r="I81" t="inlineStr"/>
-      <c r="J81" t="inlineStr"/>
-      <c r="K81" t="inlineStr"/>
+        <v>22.4479</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>rxn_21_37</t>
+          <t>rxn_20_37</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C82" t="n">
         <v>37</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Amine 37 + Acid chloride 21</t>
+          <t>Amine 37 + Acid chloride 20</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>457.4708</v>
-      </c>
-      <c r="F82" t="inlineStr"/>
-      <c r="G82" t="inlineStr"/>
-      <c r="H82" t="inlineStr"/>
-      <c r="I82" t="inlineStr"/>
-      <c r="J82" t="inlineStr"/>
-      <c r="K82" t="inlineStr"/>
+        <v>15.8582</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>rxn_22_37</t>
+          <t>rxn_21_37</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C83" t="n">
         <v>37</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Amine 37 + Acid chloride 22</t>
+          <t>Amine 37 + Acid chloride 21</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>7.5208</v>
-      </c>
-      <c r="F83" t="inlineStr"/>
-      <c r="G83" t="inlineStr"/>
-      <c r="H83" t="inlineStr"/>
-      <c r="I83" t="inlineStr"/>
-      <c r="J83" t="inlineStr"/>
-      <c r="K83" t="inlineStr"/>
+        <v>457.4708</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>rxn_23_37</t>
+          <t>rxn_22_37</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C84" t="n">
         <v>37</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Amine 37 + Acid chloride 23</t>
+          <t>Amine 37 + Acid chloride 22</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>5.8268</v>
-      </c>
-      <c r="F84" t="inlineStr"/>
-      <c r="G84" t="inlineStr"/>
-      <c r="H84" t="inlineStr"/>
-      <c r="I84" t="inlineStr"/>
-      <c r="J84" t="inlineStr"/>
-      <c r="K84" t="inlineStr"/>
+        <v>7.5208</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>rxn_24_37</t>
+          <t>rxn_23_37</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C85" t="n">
         <v>37</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Amine 37 + Acid chloride 24</t>
+          <t>Amine 37 + Acid chloride 23</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>3.1964</v>
-      </c>
-      <c r="F85" t="inlineStr"/>
-      <c r="G85" t="inlineStr"/>
-      <c r="H85" t="inlineStr"/>
-      <c r="I85" t="inlineStr"/>
-      <c r="J85" t="inlineStr"/>
-      <c r="K85" t="inlineStr"/>
+        <v>5.8268</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>rxn_25_37</t>
+          <t>rxn_24_37</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C86" t="n">
         <v>37</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Amine 37 + Acid chloride 25</t>
+          <t>Amine 37 + Acid chloride 24</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>116.673</v>
-      </c>
-      <c r="F86" t="inlineStr"/>
-      <c r="G86" t="inlineStr"/>
-      <c r="H86" t="inlineStr"/>
-      <c r="I86" t="inlineStr"/>
-      <c r="J86" t="inlineStr"/>
-      <c r="K86" t="inlineStr"/>
+        <v>3.1964</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>rxn_26_37</t>
+          <t>rxn_25_37</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C87" t="n">
         <v>37</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Amine 37 + Acid chloride 26</t>
+          <t>Amine 37 + Acid chloride 25</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>41.0131</v>
-      </c>
-      <c r="F87" t="inlineStr"/>
-      <c r="G87" t="inlineStr"/>
-      <c r="H87" t="inlineStr"/>
-      <c r="I87" t="inlineStr"/>
-      <c r="J87" t="inlineStr"/>
-      <c r="K87" t="inlineStr"/>
+        <v>116.673</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>rxn_27_37</t>
+          <t>rxn_26_37</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C88" t="n">
         <v>37</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Amine 37 + Acid chloride 27</t>
+          <t>Amine 37 + Acid chloride 26</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>64.0654</v>
-      </c>
-      <c r="F88" t="inlineStr"/>
-      <c r="G88" t="inlineStr"/>
-      <c r="H88" t="inlineStr"/>
-      <c r="I88" t="inlineStr"/>
-      <c r="J88" t="inlineStr"/>
-      <c r="K88" t="inlineStr"/>
+        <v>41.0131</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>rxn_28_37</t>
+          <t>rxn_27_37</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C89" t="n">
         <v>37</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Amine 37 + Acid chloride 28</t>
+          <t>Amine 37 + Acid chloride 27</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>10.3528</v>
-      </c>
-      <c r="F89" t="inlineStr"/>
-      <c r="G89" t="inlineStr"/>
-      <c r="H89" t="inlineStr"/>
-      <c r="I89" t="inlineStr"/>
-      <c r="J89" t="inlineStr"/>
-      <c r="K89" t="inlineStr"/>
+        <v>64.0654</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>rxn_29_37</t>
+          <t>rxn_28_37</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C90" t="n">
         <v>37</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Amine 37 + Acid chloride 29</t>
+          <t>Amine 37 + Acid chloride 28</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>5.8946</v>
-      </c>
-      <c r="F90" t="inlineStr"/>
-      <c r="G90" t="inlineStr"/>
-      <c r="H90" t="inlineStr"/>
-      <c r="I90" t="inlineStr"/>
-      <c r="J90" t="inlineStr"/>
-      <c r="K90" t="inlineStr"/>
+        <v>10.3528</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>rxn_30_37</t>
+          <t>rxn_29_37</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C91" t="n">
         <v>37</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Amine 37 + Acid chloride 30</t>
+          <t>Amine 37 + Acid chloride 29</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>32.5314</v>
-      </c>
-      <c r="F91" t="inlineStr"/>
-      <c r="G91" t="inlineStr"/>
-      <c r="H91" t="inlineStr"/>
-      <c r="I91" t="inlineStr"/>
-      <c r="J91" t="inlineStr"/>
-      <c r="K91" t="inlineStr"/>
+        <v>5.8946</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>rxn_31_37</t>
+          <t>rxn_30_37</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C92" t="n">
         <v>37</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Amine 37 + Acid chloride 31</t>
+          <t>Amine 37 + Acid chloride 30</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>13.3791</v>
-      </c>
-      <c r="F92" t="inlineStr"/>
-      <c r="G92" t="inlineStr"/>
-      <c r="H92" t="inlineStr"/>
-      <c r="I92" t="inlineStr"/>
-      <c r="J92" t="inlineStr"/>
-      <c r="K92" t="inlineStr"/>
+        <v>32.5314</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>rxn_33_37</t>
+          <t>rxn_31_37</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C93" t="n">
         <v>37</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Amine 37 + Acid chloride 33</t>
+          <t>Amine 37 + Acid chloride 31</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>10.1089</v>
-      </c>
-      <c r="F93" t="inlineStr"/>
-      <c r="G93" t="inlineStr"/>
-      <c r="H93" t="inlineStr"/>
-      <c r="I93" t="inlineStr"/>
-      <c r="J93" t="inlineStr"/>
-      <c r="K93" t="inlineStr"/>
+        <v>13.3791</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>rxn_34_37</t>
+          <t>rxn_33_37</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C94" t="n">
         <v>37</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Amine 37 + Acid chloride 34</t>
+          <t>Amine 37 + Acid chloride 33</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>8.107900000000001</v>
-      </c>
-      <c r="F94" t="inlineStr"/>
-      <c r="G94" t="inlineStr"/>
-      <c r="H94" t="inlineStr"/>
-      <c r="I94" t="inlineStr"/>
-      <c r="J94" t="inlineStr"/>
-      <c r="K94" t="inlineStr"/>
+        <v>10.1089</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>rxn_17_03</t>
+          <t>rxn_34_37</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="C95" t="n">
-        <v>3</v>
+        <v>37</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Acid chloride 17 + Amine 3</t>
+          <t>Amine 37 + Acid chloride 34</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>18.9571</v>
-      </c>
-      <c r="F95" t="n">
-        <v>30.61695809963709</v>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>medium_confidence</t>
-        </is>
-      </c>
-      <c r="H95" t="n">
-        <v>1</v>
-      </c>
-      <c r="I95" t="n">
-        <v>1</v>
-      </c>
-      <c r="J95" t="inlineStr">
-        <is>
-          <t>measurable</t>
-        </is>
-      </c>
-      <c r="K95" t="inlineStr">
-        <is>
-          <t>k_corrected &gt; 0</t>
-        </is>
+        <v>8.107900000000001</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>rxn_17_04</t>
+          <t>rxn_17_03</t>
         </is>
       </c>
       <c r="B96" t="n">
         <v>17</v>
       </c>
       <c r="C96" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Acid chloride 17 + Amine 4</t>
+          <t>Acid chloride 17 + Amine 3</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>144.1947</v>
-      </c>
-      <c r="F96" t="inlineStr"/>
-      <c r="G96" t="inlineStr"/>
-      <c r="H96" t="inlineStr"/>
-      <c r="I96" t="inlineStr"/>
+        <v>18.9571</v>
+      </c>
+      <c r="F96" t="n">
+        <v>30.61695809963709</v>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>medium_confidence</t>
+        </is>
+      </c>
+      <c r="H96" t="n">
+        <v>1</v>
+      </c>
+      <c r="I96" t="n">
+        <v>1</v>
+      </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>undetermined</t>
+          <t>measurable</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>unmeasurable workbook bin</t>
+          <t>k_corrected &gt; 0</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>rxn_17_05</t>
+          <t>rxn_17_04</t>
         </is>
       </c>
       <c r="B97" t="n">
         <v>17</v>
       </c>
       <c r="C97" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Acid chloride 17 + Amine 5</t>
+          <t>Acid chloride 17 + Amine 4</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>14.5448</v>
-      </c>
-      <c r="F97" t="n">
-        <v>31.04559478916695</v>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>medium_confidence</t>
-        </is>
-      </c>
-      <c r="H97" t="n">
-        <v>1</v>
-      </c>
-      <c r="I97" t="n">
-        <v>1</v>
+        <v>144.1947</v>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>measurable</t>
+          <t>undetermined</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>k_corrected &gt; 0</t>
+          <t>unmeasurable workbook bin</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>rxn_17_06</t>
+          <t>rxn_17_05</t>
         </is>
       </c>
       <c r="B98" t="n">
         <v>17</v>
       </c>
       <c r="C98" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Acid chloride 17 + Amine 6</t>
+          <t>Acid chloride 17 + Amine 5</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>14.4038</v>
-      </c>
-      <c r="F98" t="inlineStr"/>
-      <c r="G98" t="inlineStr"/>
-      <c r="H98" t="inlineStr"/>
-      <c r="I98" t="inlineStr"/>
+        <v>14.5448</v>
+      </c>
+      <c r="F98" t="n">
+        <v>31.04559478916695</v>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>medium_confidence</t>
+        </is>
+      </c>
+      <c r="H98" t="n">
+        <v>1</v>
+      </c>
+      <c r="I98" t="n">
+        <v>1</v>
+      </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>measurable</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>unmeasurable workbook bin</t>
+          <t>k_corrected &gt; 0</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>rxn_17_07</t>
+          <t>rxn_17_06</t>
         </is>
       </c>
       <c r="B99" t="n">
         <v>17</v>
       </c>
       <c r="C99" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Acid chloride 17 + Amine 7</t>
+          <t>Acid chloride 17 + Amine 6</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>48.7922</v>
-      </c>
-      <c r="F99" t="n">
-        <v>91.00917431192661</v>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>medium_confidence</t>
-        </is>
-      </c>
-      <c r="H99" t="n">
-        <v>1</v>
-      </c>
-      <c r="I99" t="n">
-        <v>1</v>
+        <v>14.4038</v>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>measurable</t>
+          <t>slow</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>k_corrected &gt; 0</t>
+          <t>unmeasurable workbook bin</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>rxn_17_08</t>
+          <t>rxn_17_07</t>
         </is>
       </c>
       <c r="B100" t="n">
         <v>17</v>
       </c>
       <c r="C100" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Acid chloride 17 + Amine 8</t>
+          <t>Acid chloride 17 + Amine 7</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>1.878</v>
-      </c>
-      <c r="F100" t="inlineStr"/>
-      <c r="G100" t="inlineStr"/>
-      <c r="H100" t="inlineStr"/>
-      <c r="I100" t="inlineStr"/>
+        <v>48.7922</v>
+      </c>
+      <c r="F100" t="n">
+        <v>91.00917431192661</v>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>medium_confidence</t>
+        </is>
+      </c>
+      <c r="H100" t="n">
+        <v>1</v>
+      </c>
+      <c r="I100" t="n">
+        <v>1</v>
+      </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>measurable</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>unmeasurable workbook bin</t>
+          <t>k_corrected &gt; 0</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>rxn_17_09</t>
+          <t>rxn_17_08</t>
         </is>
       </c>
       <c r="B101" t="n">
         <v>17</v>
       </c>
       <c r="C101" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Acid chloride 17 + Amine 9</t>
+          <t>Acid chloride 17 + Amine 8</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>9.0007</v>
-      </c>
-      <c r="F101" t="n">
-        <v>19.80277261683577</v>
-      </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>medium_confidence</t>
-        </is>
-      </c>
-      <c r="H101" t="n">
-        <v>1</v>
-      </c>
-      <c r="I101" t="n">
-        <v>1</v>
+        <v>1.878</v>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>measurable</t>
+          <t>slow</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>k_corrected &gt; 0</t>
+          <t>unmeasurable workbook bin</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>rxn_17_10</t>
+          <t>rxn_17_09</t>
         </is>
       </c>
       <c r="B102" t="n">
         <v>17</v>
       </c>
       <c r="C102" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Acid chloride 17 + Amine 10</t>
+          <t>Acid chloride 17 + Amine 9</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>50.6287</v>
+        <v>9.0007</v>
       </c>
       <c r="F102" t="n">
-        <v>92.7687296416938</v>
+        <v>19.80277261683577</v>
       </c>
       <c r="G102" t="inlineStr">
         <is>
@@ -4097,62 +3752,68 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>rxn_17_11</t>
+          <t>rxn_17_10</t>
         </is>
       </c>
       <c r="B103" t="n">
         <v>17</v>
       </c>
       <c r="C103" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Acid chloride 17 + Amine 11</t>
+          <t>Acid chloride 17 + Amine 10</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>1.8255</v>
-      </c>
-      <c r="F103" t="inlineStr"/>
-      <c r="G103" t="inlineStr"/>
-      <c r="H103" t="inlineStr"/>
-      <c r="I103" t="inlineStr"/>
+        <v>50.6287</v>
+      </c>
+      <c r="F103" t="n">
+        <v>92.7687296416938</v>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>medium_confidence</t>
+        </is>
+      </c>
+      <c r="H103" t="n">
+        <v>1</v>
+      </c>
+      <c r="I103" t="n">
+        <v>1</v>
+      </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>measurable</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>unmeasurable workbook bin</t>
+          <t>k_corrected &gt; 0</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>rxn_17_12</t>
+          <t>rxn_17_11</t>
         </is>
       </c>
       <c r="B104" t="n">
         <v>17</v>
       </c>
       <c r="C104" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Acid chloride 17 + Amine 12</t>
+          <t>Acid chloride 17 + Amine 11</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>4.9634</v>
-      </c>
-      <c r="F104" t="inlineStr"/>
-      <c r="G104" t="inlineStr"/>
-      <c r="H104" t="inlineStr"/>
-      <c r="I104" t="inlineStr"/>
+        <v>1.8255</v>
+      </c>
       <c r="J104" t="inlineStr">
         <is>
           <t>slow</t>
@@ -4167,74 +3828,60 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>rxn_17_13</t>
+          <t>rxn_17_12</t>
         </is>
       </c>
       <c r="B105" t="n">
         <v>17</v>
       </c>
       <c r="C105" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Acid chloride 17 + Amine 13</t>
+          <t>Acid chloride 17 + Amine 12</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>36.3382</v>
-      </c>
-      <c r="F105" t="n">
-        <v>91.42857142857149</v>
-      </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>low_confidence_order_of_magnitude</t>
-        </is>
-      </c>
-      <c r="H105" t="n">
-        <v>1</v>
-      </c>
-      <c r="I105" t="n">
-        <v>1</v>
+        <v>4.9634</v>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>measurable</t>
+          <t>slow</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>k_corrected &gt; 0</t>
+          <t>unmeasurable workbook bin</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>rxn_17_14</t>
+          <t>rxn_17_13</t>
         </is>
       </c>
       <c r="B106" t="n">
         <v>17</v>
       </c>
       <c r="C106" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Acid chloride 17 + Amine 14</t>
+          <t>Acid chloride 17 + Amine 13</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>9.9747</v>
+        <v>36.3382</v>
       </c>
       <c r="F106" t="n">
-        <v>22.55661066471877</v>
+        <v>91.42857142857149</v>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>medium_confidence</t>
+          <t>low_confidence_order_of_magnitude</t>
         </is>
       </c>
       <c r="H106" t="n">
@@ -4257,65 +3904,71 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>rxn_17_15</t>
+          <t>rxn_17_14</t>
         </is>
       </c>
       <c r="B107" t="n">
         <v>17</v>
       </c>
       <c r="C107" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Acid chloride 17 + Amine 15</t>
+          <t>Acid chloride 17 + Amine 14</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>3.1951</v>
-      </c>
-      <c r="F107" t="inlineStr"/>
-      <c r="G107" t="inlineStr"/>
-      <c r="H107" t="inlineStr"/>
-      <c r="I107" t="inlineStr"/>
+        <v>9.9747</v>
+      </c>
+      <c r="F107" t="n">
+        <v>22.55661066471877</v>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>medium_confidence</t>
+        </is>
+      </c>
+      <c r="H107" t="n">
+        <v>1</v>
+      </c>
+      <c r="I107" t="n">
+        <v>1</v>
+      </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>measurable</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>unmeasurable workbook bin</t>
+          <t>k_corrected &gt; 0</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>rxn_17_16</t>
+          <t>rxn_17_15</t>
         </is>
       </c>
       <c r="B108" t="n">
         <v>17</v>
       </c>
       <c r="C108" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Acid chloride 17 + Amine 16</t>
+          <t>Acid chloride 17 + Amine 15</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>152.342</v>
-      </c>
-      <c r="F108" t="inlineStr"/>
-      <c r="G108" t="inlineStr"/>
-      <c r="H108" t="inlineStr"/>
-      <c r="I108" t="inlineStr"/>
+        <v>3.1951</v>
+      </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>instant</t>
+          <t>slow</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
@@ -4327,110 +3980,102 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>rxn_17_17</t>
+          <t>rxn_17_16</t>
         </is>
       </c>
       <c r="B109" t="n">
         <v>17</v>
       </c>
       <c r="C109" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Acid chloride 17 + Amine 17</t>
+          <t>Acid chloride 17 + Amine 16</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6.5766</v>
-      </c>
-      <c r="F109" t="n">
-        <v>37.02352376380222</v>
-      </c>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>medium_confidence</t>
-        </is>
-      </c>
-      <c r="H109" t="n">
-        <v>1</v>
-      </c>
-      <c r="I109" t="n">
-        <v>1</v>
+        <v>152.342</v>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>measurable</t>
+          <t>instant</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>k_corrected &gt; 0</t>
+          <t>unmeasurable workbook bin</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>rxn_17_18</t>
+          <t>rxn_17_17</t>
         </is>
       </c>
       <c r="B110" t="n">
         <v>17</v>
       </c>
       <c r="C110" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Acid chloride 17 + Amine 18</t>
+          <t>Acid chloride 17 + Amine 17</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>8.727</v>
-      </c>
-      <c r="F110" t="inlineStr"/>
-      <c r="G110" t="inlineStr"/>
-      <c r="H110" t="inlineStr"/>
-      <c r="I110" t="inlineStr"/>
+        <v>6.5766</v>
+      </c>
+      <c r="F110" t="n">
+        <v>37.02352376380222</v>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>medium_confidence</t>
+        </is>
+      </c>
+      <c r="H110" t="n">
+        <v>1</v>
+      </c>
+      <c r="I110" t="n">
+        <v>1</v>
+      </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>measurable</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>unmeasurable workbook bin</t>
+          <t>k_corrected &gt; 0</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>rxn_17_19</t>
+          <t>rxn_17_18</t>
         </is>
       </c>
       <c r="B111" t="n">
         <v>17</v>
       </c>
       <c r="C111" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Acid chloride 17 + Amine 19</t>
+          <t>Acid chloride 17 + Amine 18</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>380.9524</v>
-      </c>
-      <c r="F111" t="inlineStr"/>
-      <c r="G111" t="inlineStr"/>
-      <c r="H111" t="inlineStr"/>
-      <c r="I111" t="inlineStr"/>
+        <v>8.727</v>
+      </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>instant</t>
+          <t>slow</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
@@ -4442,30 +4087,26 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>rxn_17_20</t>
+          <t>rxn_17_19</t>
         </is>
       </c>
       <c r="B112" t="n">
         <v>17</v>
       </c>
       <c r="C112" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Acid chloride 17 + Amine 20</t>
+          <t>Acid chloride 17 + Amine 19</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>1.1036</v>
-      </c>
-      <c r="F112" t="inlineStr"/>
-      <c r="G112" t="inlineStr"/>
-      <c r="H112" t="inlineStr"/>
-      <c r="I112" t="inlineStr"/>
+        <v>380.9524</v>
+      </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>instant</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
@@ -4477,154 +4118,136 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>rxn_17_21</t>
+          <t>rxn_17_20</t>
         </is>
       </c>
       <c r="B113" t="n">
         <v>17</v>
       </c>
       <c r="C113" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Acid chloride 17 + Amine 21</t>
+          <t>Acid chloride 17 + Amine 20</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>24.7273</v>
-      </c>
-      <c r="F113" t="n">
-        <v>130.4458598726115</v>
-      </c>
-      <c r="G113" t="inlineStr">
-        <is>
-          <t>medium_confidence</t>
-        </is>
-      </c>
-      <c r="H113" t="n">
-        <v>1</v>
-      </c>
-      <c r="I113" t="n">
-        <v>1</v>
+        <v>1.1036</v>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>measurable</t>
+          <t>slow</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>k_corrected &gt; 0</t>
+          <t>unmeasurable workbook bin</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>rxn_17_22</t>
+          <t>rxn_17_21</t>
         </is>
       </c>
       <c r="B114" t="n">
         <v>17</v>
       </c>
       <c r="C114" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Acid chloride 17 + Amine 22</t>
+          <t>Acid chloride 17 + Amine 21</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>61.592</v>
-      </c>
-      <c r="F114" t="inlineStr"/>
-      <c r="G114" t="inlineStr"/>
-      <c r="H114" t="inlineStr"/>
-      <c r="I114" t="inlineStr"/>
+        <v>24.7273</v>
+      </c>
+      <c r="F114" t="n">
+        <v>130.4458598726115</v>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>medium_confidence</t>
+        </is>
+      </c>
+      <c r="H114" t="n">
+        <v>1</v>
+      </c>
+      <c r="I114" t="n">
+        <v>1</v>
+      </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>instant</t>
+          <t>measurable</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>unmeasurable workbook bin</t>
+          <t>k_corrected &gt; 0</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>rxn_17_23</t>
+          <t>rxn_17_22</t>
         </is>
       </c>
       <c r="B115" t="n">
         <v>17</v>
       </c>
       <c r="C115" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Acid chloride 17 + Amine 23</t>
+          <t>Acid chloride 17 + Amine 22</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>16.489</v>
-      </c>
-      <c r="F115" t="n">
-        <v>23.1759984712402</v>
-      </c>
-      <c r="G115" t="inlineStr">
-        <is>
-          <t>medium_confidence</t>
-        </is>
-      </c>
-      <c r="H115" t="n">
-        <v>1</v>
-      </c>
-      <c r="I115" t="n">
-        <v>1</v>
+        <v>61.592</v>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>measurable</t>
+          <t>instant</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>k_corrected &gt; 0</t>
+          <t>unmeasurable workbook bin</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>rxn_17_24</t>
+          <t>rxn_17_23</t>
         </is>
       </c>
       <c r="B116" t="n">
         <v>17</v>
       </c>
       <c r="C116" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Acid chloride 17 + Amine 24</t>
+          <t>Acid chloride 17 + Amine 23</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>8.963100000000001</v>
+        <v>16.489</v>
       </c>
       <c r="F116" t="n">
-        <v>28.44444444444444</v>
+        <v>23.1759984712402</v>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>low_confidence_order_of_magnitude</t>
+          <t>medium_confidence</t>
         </is>
       </c>
       <c r="H116" t="n">
@@ -4647,109 +4270,105 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>rxn_17_25</t>
+          <t>rxn_17_24</t>
         </is>
       </c>
       <c r="B117" t="n">
         <v>17</v>
       </c>
       <c r="C117" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Acid chloride 17 + Amine 25</t>
+          <t>Acid chloride 17 + Amine 24</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>49.0021</v>
-      </c>
-      <c r="F117" t="inlineStr"/>
-      <c r="G117" t="inlineStr"/>
-      <c r="H117" t="inlineStr"/>
-      <c r="I117" t="inlineStr"/>
+        <v>8.963100000000001</v>
+      </c>
+      <c r="F117" t="n">
+        <v>28.44444444444444</v>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>low_confidence_order_of_magnitude</t>
+        </is>
+      </c>
+      <c r="H117" t="n">
+        <v>1</v>
+      </c>
+      <c r="I117" t="n">
+        <v>1</v>
+      </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>undetermined</t>
+          <t>measurable</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>unmeasurable workbook bin</t>
+          <t>k_corrected &gt; 0</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>rxn_17_26</t>
+          <t>rxn_17_25</t>
         </is>
       </c>
       <c r="B118" t="n">
         <v>17</v>
       </c>
       <c r="C118" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Acid chloride 17 + Amine 26</t>
+          <t>Acid chloride 17 + Amine 25</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>23.0558</v>
-      </c>
-      <c r="F118" t="n">
-        <v>51.19999999999998</v>
-      </c>
-      <c r="G118" t="inlineStr">
-        <is>
-          <t>low_confidence_order_of_magnitude</t>
-        </is>
-      </c>
-      <c r="H118" t="n">
-        <v>1</v>
-      </c>
-      <c r="I118" t="n">
-        <v>1</v>
+        <v>49.0021</v>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>measurable</t>
+          <t>undetermined</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>k_corrected &gt; 0</t>
+          <t>unmeasurable workbook bin</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>rxn_17_27</t>
+          <t>rxn_17_26</t>
         </is>
       </c>
       <c r="B119" t="n">
         <v>17</v>
       </c>
       <c r="C119" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Acid chloride 17 + Amine 27</t>
+          <t>Acid chloride 17 + Amine 26</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>4.9946</v>
+        <v>23.0558</v>
       </c>
       <c r="F119" t="n">
-        <v>25.13923477473397</v>
+        <v>51.19999999999998</v>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>medium_confidence</t>
+          <t>low_confidence_order_of_magnitude</t>
         </is>
       </c>
       <c r="H119" t="n">
@@ -4772,29 +4391,29 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>rxn_17_28</t>
+          <t>rxn_17_27</t>
         </is>
       </c>
       <c r="B120" t="n">
         <v>17</v>
       </c>
       <c r="C120" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Acid chloride 17 + Amine 28</t>
+          <t>Acid chloride 17 + Amine 27</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>24.9989</v>
+        <v>4.9946</v>
       </c>
       <c r="F120" t="n">
-        <v>75.29411764705881</v>
+        <v>25.13923477473397</v>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>low_confidence_order_of_magnitude</t>
+          <t>medium_confidence</t>
         </is>
       </c>
       <c r="H120" t="n">
@@ -4817,62 +4436,68 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>rxn_17_29</t>
+          <t>rxn_17_28</t>
         </is>
       </c>
       <c r="B121" t="n">
         <v>17</v>
       </c>
       <c r="C121" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Acid chloride 17 + Amine 29</t>
+          <t>Acid chloride 17 + Amine 28</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>0.1704</v>
-      </c>
-      <c r="F121" t="inlineStr"/>
-      <c r="G121" t="inlineStr"/>
-      <c r="H121" t="inlineStr"/>
-      <c r="I121" t="inlineStr"/>
+        <v>24.9989</v>
+      </c>
+      <c r="F121" t="n">
+        <v>75.29411764705881</v>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>low_confidence_order_of_magnitude</t>
+        </is>
+      </c>
+      <c r="H121" t="n">
+        <v>1</v>
+      </c>
+      <c r="I121" t="n">
+        <v>1</v>
+      </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>measurable</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>unmeasurable workbook bin</t>
+          <t>k_corrected &gt; 0</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>rxn_17_30</t>
+          <t>rxn_17_29</t>
         </is>
       </c>
       <c r="B122" t="n">
         <v>17</v>
       </c>
       <c r="C122" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Acid chloride 17 + Amine 30</t>
+          <t>Acid chloride 17 + Amine 29</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>2.6095</v>
-      </c>
-      <c r="F122" t="inlineStr"/>
-      <c r="G122" t="inlineStr"/>
-      <c r="H122" t="inlineStr"/>
-      <c r="I122" t="inlineStr"/>
+        <v>0.1704</v>
+      </c>
       <c r="J122" t="inlineStr">
         <is>
           <t>slow</t>
@@ -4887,107 +4512,99 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>rxn_17_31</t>
+          <t>rxn_17_30</t>
         </is>
       </c>
       <c r="B123" t="n">
         <v>17</v>
       </c>
       <c r="C123" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Acid chloride 17 + Amine 31</t>
+          <t>Acid chloride 17 + Amine 30</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>9.6953</v>
-      </c>
-      <c r="F123" t="n">
-        <v>27.16113867850612</v>
-      </c>
-      <c r="G123" t="inlineStr">
-        <is>
-          <t>medium_confidence</t>
-        </is>
-      </c>
-      <c r="H123" t="n">
-        <v>1</v>
-      </c>
-      <c r="I123" t="n">
-        <v>1</v>
+        <v>2.6095</v>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>measurable</t>
+          <t>slow</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>k_corrected &gt; 0</t>
+          <t>unmeasurable workbook bin</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>rxn_17_32</t>
+          <t>rxn_17_31</t>
         </is>
       </c>
       <c r="B124" t="n">
         <v>17</v>
       </c>
       <c r="C124" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Acid chloride 17 + Amine 32</t>
+          <t>Acid chloride 17 + Amine 31</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>2.3955</v>
-      </c>
-      <c r="F124" t="inlineStr"/>
-      <c r="G124" t="inlineStr"/>
-      <c r="H124" t="inlineStr"/>
-      <c r="I124" t="inlineStr"/>
+        <v>9.6953</v>
+      </c>
+      <c r="F124" t="n">
+        <v>27.16113867850612</v>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>medium_confidence</t>
+        </is>
+      </c>
+      <c r="H124" t="n">
+        <v>1</v>
+      </c>
+      <c r="I124" t="n">
+        <v>1</v>
+      </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>measurable</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>unmeasurable workbook bin</t>
+          <t>k_corrected &gt; 0</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>rxn_17_33</t>
+          <t>rxn_17_32</t>
         </is>
       </c>
       <c r="B125" t="n">
         <v>17</v>
       </c>
       <c r="C125" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Acid chloride 17 + Amine 33</t>
+          <t>Acid chloride 17 + Amine 32</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>0.526</v>
-      </c>
-      <c r="F125" t="inlineStr"/>
-      <c r="G125" t="inlineStr"/>
-      <c r="H125" t="inlineStr"/>
-      <c r="I125" t="inlineStr"/>
+        <v>2.3955</v>
+      </c>
       <c r="J125" t="inlineStr">
         <is>
           <t>slow</t>
@@ -5002,74 +4619,60 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>rxn_17_35</t>
+          <t>rxn_17_33</t>
         </is>
       </c>
       <c r="B126" t="n">
         <v>17</v>
       </c>
       <c r="C126" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Acid chloride 17 + Amine 35</t>
+          <t>Acid chloride 17 + Amine 33</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>14.1457</v>
-      </c>
-      <c r="F126" t="n">
-        <v>29.92155632256041</v>
-      </c>
-      <c r="G126" t="inlineStr">
-        <is>
-          <t>medium_confidence</t>
-        </is>
-      </c>
-      <c r="H126" t="n">
-        <v>1</v>
-      </c>
-      <c r="I126" t="n">
-        <v>1</v>
+        <v>0.526</v>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>measurable</t>
+          <t>slow</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>k_corrected &gt; 0</t>
+          <t>unmeasurable workbook bin</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>rxn_17_36</t>
+          <t>rxn_17_35</t>
         </is>
       </c>
       <c r="B127" t="n">
         <v>17</v>
       </c>
       <c r="C127" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Acid chloride 17 + Amine 36</t>
+          <t>Acid chloride 17 + Amine 35</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>0.3233</v>
+        <v>14.1457</v>
       </c>
       <c r="F127" t="n">
-        <v>21.33333333333334</v>
+        <v>29.92155632256041</v>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>low_confidence_order_of_magnitude</t>
+          <t>medium_confidence</t>
         </is>
       </c>
       <c r="H127" t="n">
@@ -5092,704 +4695,593 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>rxn_01_38</t>
+          <t>rxn_17_36</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="C128" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Acid chloride 1 + Amine 38</t>
+          <t>Acid chloride 17 + Amine 36</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>2191.3634</v>
-      </c>
-      <c r="F128" t="inlineStr"/>
-      <c r="G128" t="inlineStr"/>
-      <c r="H128" t="inlineStr"/>
-      <c r="I128" t="inlineStr"/>
-      <c r="J128" t="inlineStr"/>
-      <c r="K128" t="inlineStr"/>
+        <v>0.3233</v>
+      </c>
+      <c r="F128" t="n">
+        <v>21.33333333333334</v>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>low_confidence_order_of_magnitude</t>
+        </is>
+      </c>
+      <c r="H128" t="n">
+        <v>1</v>
+      </c>
+      <c r="I128" t="n">
+        <v>1</v>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>measurable</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>k_corrected &gt; 0</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>rxn_01_39</t>
+          <t>rxn_01_38</t>
         </is>
       </c>
       <c r="B129" t="n">
         <v>1</v>
       </c>
       <c r="C129" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Acid chloride 1 + Amine 39</t>
+          <t>Acid chloride 1 + Amine 38</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>138.6262</v>
-      </c>
-      <c r="F129" t="inlineStr"/>
-      <c r="G129" t="inlineStr"/>
-      <c r="H129" t="inlineStr"/>
-      <c r="I129" t="inlineStr"/>
-      <c r="J129" t="inlineStr"/>
-      <c r="K129" t="inlineStr"/>
+        <v>2191.3634</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>rxn_01_40</t>
+          <t>rxn_01_39</t>
         </is>
       </c>
       <c r="B130" t="n">
         <v>1</v>
       </c>
       <c r="C130" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Acid chloride 1 + Amine 40</t>
+          <t>Acid chloride 1 + Amine 39</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>12.673</v>
-      </c>
-      <c r="F130" t="inlineStr"/>
-      <c r="G130" t="inlineStr"/>
-      <c r="H130" t="inlineStr"/>
-      <c r="I130" t="inlineStr"/>
-      <c r="J130" t="inlineStr"/>
-      <c r="K130" t="inlineStr"/>
+        <v>138.6262</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>rxn_01_41</t>
+          <t>rxn_01_40</t>
         </is>
       </c>
       <c r="B131" t="n">
         <v>1</v>
       </c>
       <c r="C131" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Acid chloride 1 + Amine 41</t>
+          <t>Acid chloride 1 + Amine 40</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>1.434</v>
-      </c>
-      <c r="F131" t="inlineStr"/>
-      <c r="G131" t="inlineStr"/>
-      <c r="H131" t="inlineStr"/>
-      <c r="I131" t="inlineStr"/>
-      <c r="J131" t="inlineStr"/>
-      <c r="K131" t="inlineStr"/>
+        <v>12.673</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>rxn_01_42</t>
+          <t>rxn_01_41</t>
         </is>
       </c>
       <c r="B132" t="n">
         <v>1</v>
       </c>
       <c r="C132" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Acid chloride 1 + Amine 42</t>
+          <t>Acid chloride 1 + Amine 41</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>1.2271</v>
-      </c>
-      <c r="F132" t="inlineStr"/>
-      <c r="G132" t="inlineStr"/>
-      <c r="H132" t="inlineStr"/>
-      <c r="I132" t="inlineStr"/>
-      <c r="J132" t="inlineStr"/>
-      <c r="K132" t="inlineStr"/>
+        <v>1.434</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>rxn_01_43</t>
+          <t>rxn_01_42</t>
         </is>
       </c>
       <c r="B133" t="n">
         <v>1</v>
       </c>
       <c r="C133" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Acid chloride 1 + Amine 43</t>
+          <t>Acid chloride 1 + Amine 42</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>197.6356</v>
-      </c>
-      <c r="F133" t="inlineStr"/>
-      <c r="G133" t="inlineStr"/>
-      <c r="H133" t="inlineStr"/>
-      <c r="I133" t="inlineStr"/>
-      <c r="J133" t="inlineStr"/>
-      <c r="K133" t="inlineStr"/>
+        <v>1.2271</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>rxn_01_44</t>
+          <t>rxn_01_43</t>
         </is>
       </c>
       <c r="B134" t="n">
         <v>1</v>
       </c>
       <c r="C134" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Acid chloride 1 + Amine 44</t>
+          <t>Acid chloride 1 + Amine 43</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>43.4062</v>
-      </c>
-      <c r="F134" t="inlineStr"/>
-      <c r="G134" t="inlineStr"/>
-      <c r="H134" t="inlineStr"/>
-      <c r="I134" t="inlineStr"/>
-      <c r="J134" t="inlineStr"/>
-      <c r="K134" t="inlineStr"/>
+        <v>197.6356</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>rxn_01_45</t>
+          <t>rxn_01_44</t>
         </is>
       </c>
       <c r="B135" t="n">
         <v>1</v>
       </c>
       <c r="C135" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Acid chloride 1 + Amine 45</t>
+          <t>Acid chloride 1 + Amine 44</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>3.5339</v>
-      </c>
-      <c r="F135" t="inlineStr"/>
-      <c r="G135" t="inlineStr"/>
-      <c r="H135" t="inlineStr"/>
-      <c r="I135" t="inlineStr"/>
-      <c r="J135" t="inlineStr"/>
-      <c r="K135" t="inlineStr"/>
+        <v>43.4062</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>rxn_01_46</t>
+          <t>rxn_01_45</t>
         </is>
       </c>
       <c r="B136" t="n">
         <v>1</v>
       </c>
       <c r="C136" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Acid chloride 1 + Amine 46</t>
+          <t>Acid chloride 1 + Amine 45</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>10.9399</v>
-      </c>
-      <c r="F136" t="inlineStr"/>
-      <c r="G136" t="inlineStr"/>
-      <c r="H136" t="inlineStr"/>
-      <c r="I136" t="inlineStr"/>
-      <c r="J136" t="inlineStr"/>
-      <c r="K136" t="inlineStr"/>
+        <v>3.5339</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>rxn_01_47</t>
+          <t>rxn_01_46</t>
         </is>
       </c>
       <c r="B137" t="n">
         <v>1</v>
       </c>
       <c r="C137" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Acid chloride 1 + Amine 47</t>
+          <t>Acid chloride 1 + Amine 46</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>10.3811</v>
-      </c>
-      <c r="F137" t="inlineStr"/>
-      <c r="G137" t="inlineStr"/>
-      <c r="H137" t="inlineStr"/>
-      <c r="I137" t="inlineStr"/>
-      <c r="J137" t="inlineStr"/>
-      <c r="K137" t="inlineStr"/>
+        <v>10.9399</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>rxn_01_48</t>
+          <t>rxn_01_47</t>
         </is>
       </c>
       <c r="B138" t="n">
         <v>1</v>
       </c>
       <c r="C138" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Acid chloride 1 + Amine 48</t>
+          <t>Acid chloride 1 + Amine 47</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>7.4106</v>
-      </c>
-      <c r="F138" t="inlineStr"/>
-      <c r="G138" t="inlineStr"/>
-      <c r="H138" t="inlineStr"/>
-      <c r="I138" t="inlineStr"/>
-      <c r="J138" t="inlineStr"/>
-      <c r="K138" t="inlineStr"/>
+        <v>10.3811</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>rxn_32_03</t>
+          <t>rxn_01_48</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="C139" t="n">
-        <v>3</v>
+        <v>48</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Amine 3 + Acid chloride 32</t>
+          <t>Acid chloride 1 + Amine 48</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>408.8299</v>
-      </c>
-      <c r="F139" t="inlineStr"/>
-      <c r="G139" t="inlineStr"/>
-      <c r="H139" t="inlineStr"/>
-      <c r="I139" t="inlineStr"/>
-      <c r="J139" t="inlineStr"/>
-      <c r="K139" t="inlineStr"/>
+        <v>7.4106</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>rxn_33_03</t>
+          <t>rxn_32_03</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C140" t="n">
         <v>3</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Amine 3 + Acid chloride 33</t>
+          <t>Amine 3 + Acid chloride 32</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>7.266</v>
-      </c>
-      <c r="F140" t="inlineStr"/>
-      <c r="G140" t="inlineStr"/>
-      <c r="H140" t="inlineStr"/>
-      <c r="I140" t="inlineStr"/>
-      <c r="J140" t="inlineStr"/>
-      <c r="K140" t="inlineStr"/>
+        <v>408.8299</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>rxn_34_03</t>
+          <t>rxn_33_03</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C141" t="n">
         <v>3</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Amine 3 + Acid chloride 34</t>
+          <t>Amine 3 + Acid chloride 33</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>3.683</v>
-      </c>
-      <c r="F141" t="inlineStr"/>
-      <c r="G141" t="inlineStr"/>
-      <c r="H141" t="inlineStr"/>
-      <c r="I141" t="inlineStr"/>
-      <c r="J141" t="inlineStr"/>
-      <c r="K141" t="inlineStr"/>
+        <v>7.266</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>rxn_35_03</t>
+          <t>rxn_34_03</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C142" t="n">
         <v>3</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Amine 3 + Acid chloride 35</t>
+          <t>Amine 3 + Acid chloride 34</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>190.8929</v>
-      </c>
-      <c r="F142" t="inlineStr"/>
-      <c r="G142" t="inlineStr"/>
-      <c r="H142" t="inlineStr"/>
-      <c r="I142" t="inlineStr"/>
-      <c r="J142" t="inlineStr"/>
-      <c r="K142" t="inlineStr"/>
+        <v>3.683</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>rxn_36_03</t>
+          <t>rxn_35_03</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C143" t="n">
         <v>3</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Amine 3 + Acid chloride 36</t>
+          <t>Amine 3 + Acid chloride 35</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>493.851</v>
-      </c>
-      <c r="F143" t="inlineStr"/>
-      <c r="G143" t="inlineStr"/>
-      <c r="H143" t="inlineStr"/>
-      <c r="I143" t="inlineStr"/>
-      <c r="J143" t="inlineStr"/>
-      <c r="K143" t="inlineStr"/>
+        <v>190.8929</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>rxn_37_03</t>
+          <t>rxn_36_03</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C144" t="n">
         <v>3</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Amine 3 + Acid chloride 37</t>
+          <t>Amine 3 + Acid chloride 36</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>79.4808</v>
-      </c>
-      <c r="F144" t="inlineStr"/>
-      <c r="G144" t="inlineStr"/>
-      <c r="H144" t="inlineStr"/>
-      <c r="I144" t="inlineStr"/>
-      <c r="J144" t="inlineStr"/>
-      <c r="K144" t="inlineStr"/>
+        <v>493.851</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>rxn_38_03</t>
+          <t>rxn_37_03</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C145" t="n">
         <v>3</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Amine 3 + Acid chloride 38</t>
+          <t>Amine 3 + Acid chloride 37</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>159.8956</v>
-      </c>
-      <c r="F145" t="inlineStr"/>
-      <c r="G145" t="inlineStr"/>
-      <c r="H145" t="inlineStr"/>
-      <c r="I145" t="inlineStr"/>
-      <c r="J145" t="inlineStr"/>
-      <c r="K145" t="inlineStr"/>
+        <v>79.4808</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>rxn_39_03</t>
+          <t>rxn_38_03</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C146" t="n">
         <v>3</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Amine 3 + Acid chloride 39</t>
+          <t>Amine 3 + Acid chloride 38</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>231.3762</v>
-      </c>
-      <c r="F146" t="inlineStr"/>
-      <c r="G146" t="inlineStr"/>
-      <c r="H146" t="inlineStr"/>
-      <c r="I146" t="inlineStr"/>
-      <c r="J146" t="inlineStr"/>
-      <c r="K146" t="inlineStr"/>
+        <v>159.8956</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>rxn_40_03</t>
+          <t>rxn_39_03</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C147" t="n">
         <v>3</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Amine 3 + Acid chloride 40</t>
+          <t>Amine 3 + Acid chloride 39</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>7389.5464</v>
-      </c>
-      <c r="F147" t="inlineStr"/>
-      <c r="G147" t="inlineStr"/>
-      <c r="H147" t="inlineStr"/>
-      <c r="I147" t="inlineStr"/>
-      <c r="J147" t="inlineStr"/>
-      <c r="K147" t="inlineStr"/>
+        <v>231.3762</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>rxn_41_03</t>
+          <t>rxn_40_03</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C148" t="n">
         <v>3</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Amine 3 + Acid chloride 41</t>
+          <t>Amine 3 + Acid chloride 40</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>6718.5892</v>
-      </c>
-      <c r="F148" t="inlineStr"/>
-      <c r="G148" t="inlineStr"/>
-      <c r="H148" t="inlineStr"/>
-      <c r="I148" t="inlineStr"/>
-      <c r="J148" t="inlineStr"/>
-      <c r="K148" t="inlineStr"/>
+        <v>7389.5464</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>rxn_42_03</t>
+          <t>rxn_41_03</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C149" t="n">
         <v>3</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Amine 3 + Acid chloride 42</t>
+          <t>Amine 3 + Acid chloride 41</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>29.2274</v>
-      </c>
-      <c r="F149" t="inlineStr"/>
-      <c r="G149" t="inlineStr"/>
-      <c r="H149" t="inlineStr"/>
-      <c r="I149" t="inlineStr"/>
-      <c r="J149" t="inlineStr"/>
-      <c r="K149" t="inlineStr"/>
+        <v>6718.5892</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>rxn_43_03</t>
+          <t>rxn_42_03</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C150" t="n">
         <v>3</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Amine 3 + Acid chloride 43</t>
+          <t>Amine 3 + Acid chloride 42</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>67.2141</v>
-      </c>
-      <c r="F150" t="inlineStr"/>
-      <c r="G150" t="inlineStr"/>
-      <c r="H150" t="inlineStr"/>
-      <c r="I150" t="inlineStr"/>
-      <c r="J150" t="inlineStr"/>
-      <c r="K150" t="inlineStr"/>
+        <v>29.2274</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>rxn_44_03</t>
+          <t>rxn_43_03</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C151" t="n">
         <v>3</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Amine 3 + Acid chloride 44</t>
+          <t>Amine 3 + Acid chloride 43</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>2.9579</v>
-      </c>
-      <c r="F151" t="inlineStr"/>
-      <c r="G151" t="inlineStr"/>
-      <c r="H151" t="inlineStr"/>
-      <c r="I151" t="inlineStr"/>
-      <c r="J151" t="inlineStr"/>
-      <c r="K151" t="inlineStr"/>
+        <v>67.2141</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>rxn_45_03</t>
+          <t>rxn_44_03</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C152" t="n">
         <v>3</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Amine 3 + Acid chloride 45</t>
+          <t>Amine 3 + Acid chloride 44</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>1158</v>
-      </c>
-      <c r="F152" t="inlineStr"/>
-      <c r="G152" t="inlineStr"/>
-      <c r="H152" t="inlineStr"/>
-      <c r="I152" t="inlineStr"/>
-      <c r="J152" t="inlineStr"/>
-      <c r="K152" t="inlineStr"/>
+        <v>2.9579</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>rxn_46_03</t>
+          <t>rxn_45_03</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C153" t="n">
         <v>3</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
+          <t>Amine 3 + Acid chloride 45</t>
+        </is>
+      </c>
+      <c r="E153" t="n">
+        <v>1158.5483</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>rxn_46_03</t>
+        </is>
+      </c>
+      <c r="B154" t="n">
+        <v>46</v>
+      </c>
+      <c r="C154" t="n">
+        <v>3</v>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
           <t>Amine 3 + Acid chloride 46</t>
         </is>
       </c>
-      <c r="E153" t="n">
-        <v>3939</v>
-      </c>
-      <c r="F153" t="inlineStr"/>
-      <c r="G153" t="inlineStr"/>
-      <c r="H153" t="inlineStr"/>
-      <c r="I153" t="inlineStr"/>
-      <c r="J153" t="inlineStr"/>
-      <c r="K153" t="inlineStr"/>
+      <c r="E154" t="n">
+        <v>3939.9413</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
